--- a/data/trans_camb/P57GLOBAL_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,68; -7,71</t>
+          <t>-18,13; -7,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 6,86</t>
+          <t>-1,97; 6,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,44; -13,32</t>
+          <t>-24,07; -12,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -0,23</t>
+          <t>-9,55; 0,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 11,83</t>
+          <t>3,12; 11,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,51; -10,5</t>
+          <t>-19,06; -10,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -5,6</t>
+          <t>-12,3; -5,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,26</t>
+          <t>1,9; 7,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,24; -13,16</t>
+          <t>-20,17; -13,37</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,37; -10,3</t>
+          <t>-23,08; -10,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 9,12</t>
+          <t>-2,46; 9,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,95; -17,73</t>
+          <t>-30,59; -16,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -0,29</t>
+          <t>-12,02; 0,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 15,75</t>
+          <t>3,8; 15,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,63; -13,92</t>
+          <t>-24,3; -13,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -7,35</t>
+          <t>-15,67; -7,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 10,91</t>
+          <t>2,4; 10,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,8; -17,38</t>
+          <t>-25,81; -17,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 2,94</t>
+          <t>-5,78; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 15,4</t>
+          <t>7,35; 14,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,09; -4,07</t>
+          <t>-46,99; -3,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,64</t>
+          <t>-3,15; 4,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,16; 16,3</t>
+          <t>8,52; 15,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -2,41</t>
+          <t>-9,98; -2,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,67</t>
+          <t>-3,11; 2,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,19; 14,69</t>
+          <t>9,29; 14,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-34,71; -4,59</t>
+          <t>-33,32; -4,62</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 4,38</t>
+          <t>-8,07; 3,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 22,74</t>
+          <t>10,23; 22,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,43; -5,95</t>
+          <t>-67,3; -5,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 6,53</t>
+          <t>-4,23; 6,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 22,96</t>
+          <t>11,18; 22,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -3,38</t>
+          <t>-13,15; -2,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,8</t>
+          <t>-4,24; 3,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,34; 20,83</t>
+          <t>12,63; 21,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,45; -6,38</t>
+          <t>-46,64; -6,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 6,39</t>
+          <t>-3,46; 7,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,64; 25,79</t>
+          <t>16,95; 26,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 7,21</t>
+          <t>-4,71; 7,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 7,1</t>
+          <t>-2,48; 7,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 22,49</t>
+          <t>13,8; 22,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 0,51</t>
+          <t>-14,19; 0,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 5,45</t>
+          <t>-1,63; 5,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 23,4</t>
+          <t>16,46; 23,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,13</t>
+          <t>-7,1; 2,0</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 10,38</t>
+          <t>-5,2; 12,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,5; 42,11</t>
+          <t>24,59; 42,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 11,59</t>
+          <t>-6,84; 12,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 10,89</t>
+          <t>-3,62; 10,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,63; 35,04</t>
+          <t>19,71; 34,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 0,69</t>
+          <t>-20,57; 0,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 8,51</t>
+          <t>-2,37; 8,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,44; 36,51</t>
+          <t>24,33; 36,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 3,19</t>
+          <t>-10,45; 3,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,35</t>
+          <t>0,5; 8,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 14,52</t>
+          <t>6,87; 14,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,54; -3,4</t>
+          <t>-12,62; -3,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 14,99</t>
+          <t>7,7; 15,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 15,63</t>
+          <t>8,21; 15,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,05; -7,16</t>
+          <t>-25,14; -6,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 10,88</t>
+          <t>5,18; 10,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 13,88</t>
+          <t>8,38; 13,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -7,06</t>
+          <t>-17,08; -6,72</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 12,25</t>
+          <t>0,68; 12,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,17; 21,34</t>
+          <t>9,71; 21,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -4,93</t>
+          <t>-17,77; -5,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,89; 21,96</t>
+          <t>10,5; 22,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,74; 22,56</t>
+          <t>11,29; 23,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,63; -10,22</t>
+          <t>-35,04; -10,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,72; 15,86</t>
+          <t>7,25; 15,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,98; 20,28</t>
+          <t>11,59; 20,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -10,12</t>
+          <t>-23,98; -9,69</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,68</t>
+          <t>-3,95; 0,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,39; 13,82</t>
+          <t>9,49; 13,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-25,26; -6,42</t>
+          <t>-26,27; -6,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,2</t>
+          <t>1,11; 5,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,43; 14,45</t>
+          <t>10,49; 14,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -6,81</t>
+          <t>-14,6; -7,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,31</t>
+          <t>-0,85; 2,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,6; 13,41</t>
+          <t>10,54; 13,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,1; -7,57</t>
+          <t>-19,12; -7,77</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,98</t>
+          <t>-5,51; 1,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13,08; 20,09</t>
+          <t>13,19; 19,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-35,96; -9,21</t>
+          <t>-37,49; -9,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,34; 7,32</t>
+          <t>1,5; 7,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,24; 20,41</t>
+          <t>14,2; 20,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -9,53</t>
+          <t>-20,15; -10,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,28</t>
+          <t>-1,16; 3,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14,65; 18,99</t>
+          <t>14,59; 18,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,82; -10,67</t>
+          <t>-26,85; -10,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57GLOBAL_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57GLOBAL_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-18,59</t>
+          <t>-17,66</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,92</t>
+          <t>-14,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-16,71</t>
+          <t>-16,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -7,9</t>
+          <t>-17,56; -8,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 6,98</t>
+          <t>-2,12; 6,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,07; -12,65</t>
+          <t>-23,32; -12,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 0,08</t>
+          <t>-10,04; -0,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,65</t>
+          <t>3,56; 11,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,06; -10,19</t>
+          <t>-18,9; -9,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,3; -5,29</t>
+          <t>-11,9; -5,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,94</t>
+          <t>1,95; 8,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,17; -13,37</t>
+          <t>-19,5; -12,82</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-24,1%</t>
+          <t>-22,88%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-19,29%</t>
+          <t>-18,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-21,63%</t>
+          <t>-20,8%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,08; -10,55</t>
+          <t>-22,25; -10,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 9,36</t>
+          <t>-2,65; 9,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,59; -16,89</t>
+          <t>-29,63; -16,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 0,12</t>
+          <t>-12,63; -0,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 15,41</t>
+          <t>4,52; 15,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,3; -13,58</t>
+          <t>-23,83; -13,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,67; -7,11</t>
+          <t>-15,19; -6,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,51</t>
+          <t>2,57; 10,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,81; -17,86</t>
+          <t>-24,87; -16,92</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-18,76</t>
+          <t>-4,28</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,12</t>
+          <t>-5,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-13,37</t>
+          <t>-4,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 2,61</t>
+          <t>-5,93; 2,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 14,97</t>
+          <t>7,41; 15,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-46,99; -3,83</t>
+          <t>-8,48; 0,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 4,97</t>
+          <t>-3,43; 5,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,52; 15,78</t>
+          <t>9,09; 16,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -2,16</t>
+          <t>-8,83; -1,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,66</t>
+          <t>-3,07; 2,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,29; 14,81</t>
+          <t>9,43; 14,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-33,32; -4,62</t>
+          <t>-7,73; -1,69</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-26,73%</t>
+          <t>-6,1%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-8,28%</t>
+          <t>-6,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,55%</t>
+          <t>-6,46%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 3,86</t>
+          <t>-8,18; 4,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 22,27</t>
+          <t>10,32; 22,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,3; -5,7</t>
+          <t>-11,76; 0,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 6,89</t>
+          <t>-4,44; 7,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 22,06</t>
+          <t>11,94; 23,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,15; -2,99</t>
+          <t>-11,61; -1,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 3,77</t>
+          <t>-4,2; 4,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,63; 21,07</t>
+          <t>12,74; 20,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,64; -6,5</t>
+          <t>-10,48; -2,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,05</t>
+          <t>-1,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 7,45</t>
+          <t>-3,65; 7,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,95; 26,29</t>
+          <t>17,16; 25,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 7,6</t>
+          <t>-2,53; 8,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 7,12</t>
+          <t>-2,63; 7,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 22,15</t>
+          <t>13,88; 22,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 0,29</t>
+          <t>-6,25; 3,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 5,59</t>
+          <t>-1,54; 5,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,46; 23,05</t>
+          <t>16,73; 23,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 2,0</t>
+          <t>-3,03; 3,85</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-7,47%</t>
+          <t>-2,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,69%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 12,19</t>
+          <t>-5,43; 11,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,59; 42,76</t>
+          <t>25,5; 42,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 12,19</t>
+          <t>-3,83; 13,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 10,95</t>
+          <t>-3,8; 12,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,71; 34,29</t>
+          <t>19,85; 35,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 0,43</t>
+          <t>-8,79; 4,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 8,85</t>
+          <t>-2,3; 8,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,33; 36,1</t>
+          <t>24,26; 35,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 3,08</t>
+          <t>-4,49; 6,0</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-8,05</t>
+          <t>-6,42</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-12,55</t>
+          <t>-7,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-10,47</t>
+          <t>-6,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 8,53</t>
+          <t>0,2; 8,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 14,53</t>
+          <t>6,63; 14,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -3,54</t>
+          <t>-10,71; -2,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,7; 15,34</t>
+          <t>7,46; 14,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 15,69</t>
+          <t>7,93; 15,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,14; -6,92</t>
+          <t>-11,42; -3,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,84</t>
+          <t>5,25; 10,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 13,9</t>
+          <t>8,55; 13,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,08; -6,72</t>
+          <t>-9,66; -4,11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-11,52%</t>
+          <t>-9,2%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-17,79%</t>
+          <t>-10,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,92%</t>
+          <t>-9,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,6</t>
+          <t>0,29; 12,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,71; 21,51</t>
+          <t>9,27; 21,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -5,22</t>
+          <t>-14,82; -2,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,5; 22,58</t>
+          <t>10,25; 21,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,29; 23,08</t>
+          <t>10,79; 22,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -10,0</t>
+          <t>-15,89; -5,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 15,75</t>
+          <t>7,34; 15,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,59; 20,22</t>
+          <t>12,03; 20,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,98; -9,69</t>
+          <t>-13,44; -5,94</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-11,9</t>
+          <t>-6,1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-9,75</t>
+          <t>-6,98</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-10,85</t>
+          <t>-6,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,71</t>
+          <t>-3,8; 0,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,74</t>
+          <t>9,25; 13,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-26,27; -6,62</t>
+          <t>-8,36; -3,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,15</t>
+          <t>1,0; 5,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,49; 14,48</t>
+          <t>10,56; 14,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -7,22</t>
+          <t>-8,99; -4,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,35</t>
+          <t>-0,68; 2,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,54; 13,35</t>
+          <t>10,47; 13,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-19,12; -7,77</t>
+          <t>-8,32; -4,99</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-16,89%</t>
+          <t>-8,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-13,49%</t>
+          <t>-9,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,2%</t>
+          <t>-9,16%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,04</t>
+          <t>-5,29; 1,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,84</t>
+          <t>12,92; 19,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,49; -9,43</t>
+          <t>-11,67; -5,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,2</t>
+          <t>1,37; 7,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,2; 20,41</t>
+          <t>14,37; 20,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,15; -10,19</t>
+          <t>-12,3; -6,94</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,3</t>
+          <t>-0,94; 3,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14,59; 18,99</t>
+          <t>14,49; 18,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -10,96</t>
+          <t>-11,53; -7,05</t>
         </is>
       </c>
     </row>
